--- a/public/plantilla-com-evaluacion.xlsx
+++ b/public/plantilla-com-evaluacion.xlsx
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -196,7 +196,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -294,6 +294,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6FAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -599,7 +604,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
@@ -724,34 +729,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -937,7 +942,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -946,7 +951,7 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -967,28 +972,28 @@
     <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1101,20 +1106,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11405,43 +11435,43 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>862393</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>862393</colOff>
+      <row>5</row>
+      <rowOff>131445</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11743,13 +11773,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" style="67" min="1" max="1"/>
-    <col width="13" customWidth="1" style="67" min="2" max="3"/>
+    <col width="13" customWidth="1" style="67" min="2" max="2"/>
     <col width="13" customWidth="1" style="67" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="67" min="4" max="4"/>
     <col width="10" customWidth="1" style="67" min="5" max="5"/>
@@ -11807,7 +11838,7 @@
         </is>
       </c>
       <c r="I5" s="29" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="188" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
@@ -11826,7 +11857,7 @@
         </is>
       </c>
       <c r="I6" s="29" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="188" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
@@ -11845,7 +11876,7 @@
       <c r="G7" s="68" t="n"/>
       <c r="H7" s="68" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="188" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
@@ -11864,7 +11895,7 @@
       <c r="G8" s="68" t="n"/>
       <c r="H8" s="68" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="188" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
@@ -11877,7 +11908,7 @@
       <c r="L8" s="32" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="67">
-      <c r="A9" s="121" t="inlineStr">
+      <c r="A9" s="189" t="inlineStr">
         <is>
           <t>Se evalúa con lo que pasó: entregas a tiempo, lo recibido y el trato comercial</t>
         </is>
@@ -11913,7 +11944,7 @@
       <c r="L10" s="17" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="67">
-      <c r="A11" s="122" t="inlineStr">
+      <c r="A11" s="190" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
@@ -11931,7 +11962,7 @@
       <c r="L11" s="163" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="67">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="190" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
@@ -11942,7 +11973,7 @@
       <c r="E12" s="162" t="n"/>
       <c r="F12" s="162" t="n"/>
       <c r="G12" s="163" t="n"/>
-      <c r="H12" s="122" t="inlineStr">
+      <c r="H12" s="190" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
@@ -11953,7 +11984,7 @@
       <c r="L12" s="163" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="67">
-      <c r="A13" s="122" t="inlineStr">
+      <c r="A13" s="190" t="inlineStr">
         <is>
           <t>Tipo de evaluación</t>
         </is>
@@ -11964,7 +11995,7 @@
       <c r="E13" s="162" t="n"/>
       <c r="F13" s="162" t="n"/>
       <c r="G13" s="163" t="n"/>
-      <c r="H13" s="122" t="inlineStr">
+      <c r="H13" s="190" t="inlineStr">
         <is>
           <t>Suministro o servicio evaluado</t>
         </is>
@@ -11975,7 +12006,7 @@
       <c r="L13" s="163" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="67">
-      <c r="A14" s="122" t="inlineStr">
+      <c r="A14" s="190" t="inlineStr">
         <is>
           <t>Periodo evaluado desde</t>
         </is>
@@ -11983,14 +12014,14 @@
       <c r="B14" s="32" t="n"/>
       <c r="C14" s="161" t="n"/>
       <c r="D14" s="163" t="n"/>
-      <c r="E14" s="122" t="inlineStr">
+      <c r="E14" s="190" t="inlineStr">
         <is>
           <t>Hasta</t>
         </is>
       </c>
       <c r="F14" s="32" t="n"/>
       <c r="G14" s="161" t="n"/>
-      <c r="H14" s="122" t="inlineStr">
+      <c r="H14" s="190" t="inlineStr">
         <is>
           <t>Fecha de evaluación</t>
         </is>
@@ -12019,12 +12050,12 @@
       <c r="L15" s="17" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1" s="67">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="191" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B16" s="124" t="inlineStr">
+      <c r="B16" s="192" t="inlineStr">
         <is>
           <t>Criterio de evaluación</t>
         </is>
@@ -12033,18 +12064,18 @@
       <c r="D16" s="31" t="n"/>
       <c r="E16" s="31" t="n"/>
       <c r="F16" s="32" t="n"/>
-      <c r="G16" s="124" t="inlineStr">
+      <c r="G16" s="192" t="inlineStr">
         <is>
           <t>Peso (%)</t>
         </is>
       </c>
-      <c r="H16" s="124" t="inlineStr">
+      <c r="H16" s="192" t="inlineStr">
         <is>
           <t>Calificación (1 a 5)</t>
         </is>
       </c>
       <c r="I16" s="32" t="n"/>
-      <c r="J16" s="124" t="inlineStr">
+      <c r="J16" s="192" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -12185,7 +12216,7 @@
       <c r="L22" s="172" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1" s="67">
-      <c r="A23" s="124" t="inlineStr">
+      <c r="A23" s="192" t="inlineStr">
         <is>
           <t>TOTAL (sobre 100 puntos)</t>
         </is>
@@ -12199,7 +12230,7 @@
         <f>SUM(G17:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="187">
+      <c r="H23" s="193">
         <f>IF(COUNT(H17:H22)=6,ROUND(SUMPRODUCT(G17:G22,H17:H22)/5,1),"")</f>
         <v/>
       </c>
@@ -12230,7 +12261,7 @@
       <c r="L24" s="17" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="67">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="190" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
@@ -12241,7 +12272,7 @@
       <c r="E25" s="162" t="n"/>
       <c r="F25" s="162" t="n"/>
       <c r="G25" s="163" t="n"/>
-      <c r="H25" s="122" t="inlineStr">
+      <c r="H25" s="190" t="inlineStr">
         <is>
           <t>Fecha de próxima evaluación</t>
         </is>
@@ -12252,7 +12283,7 @@
       <c r="L25" s="163" t="n"/>
     </row>
     <row r="26" ht="45" customHeight="1" s="67">
-      <c r="A26" s="122" t="inlineStr">
+      <c r="A26" s="190" t="inlineStr">
         <is>
           <t>Fortalezas observadas</t>
         </is>
@@ -12270,7 +12301,7 @@
       <c r="L26" s="163" t="n"/>
     </row>
     <row r="27" ht="45" customHeight="1" s="67">
-      <c r="A27" s="122" t="inlineStr">
+      <c r="A27" s="190" t="inlineStr">
         <is>
           <t>Aspectos a mejorar y acuerdos</t>
         </is>
@@ -12306,7 +12337,7 @@
       <c r="L28" s="17" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="67">
-      <c r="A29" s="130" t="inlineStr">
+      <c r="A29" s="194" t="inlineStr">
         <is>
           <t>EVALÚA — COMPRAS</t>
         </is>
@@ -12314,7 +12345,7 @@
       <c r="B29" s="31" t="n"/>
       <c r="C29" s="31" t="n"/>
       <c r="D29" s="32" t="n"/>
-      <c r="E29" s="130" t="inlineStr">
+      <c r="E29" s="194" t="inlineStr">
         <is>
           <t>REVISA — RESIDENTE DE OBRA</t>
         </is>
@@ -12322,7 +12353,7 @@
       <c r="F29" s="31" t="n"/>
       <c r="G29" s="31" t="n"/>
       <c r="H29" s="32" t="n"/>
-      <c r="I29" s="130" t="inlineStr">
+      <c r="I29" s="194" t="inlineStr">
         <is>
           <t>VO.BO. — GERENCIA</t>
         </is>
@@ -12332,7 +12363,7 @@
       <c r="L29" s="32" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1" s="67">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="195" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12340,7 +12371,7 @@
       <c r="B30" s="17" t="n"/>
       <c r="C30" s="170" t="n"/>
       <c r="D30" s="172" t="n"/>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="195" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12348,7 +12379,7 @@
       <c r="F30" s="17" t="n"/>
       <c r="G30" s="170" t="n"/>
       <c r="H30" s="172" t="n"/>
-      <c r="I30" s="18" t="inlineStr">
+      <c r="I30" s="195" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12358,7 +12389,7 @@
       <c r="L30" s="172" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1" s="67">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="195" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12366,7 +12397,7 @@
       <c r="B31" s="17" t="n"/>
       <c r="C31" s="170" t="n"/>
       <c r="D31" s="172" t="n"/>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="195" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12374,7 +12405,7 @@
       <c r="F31" s="17" t="n"/>
       <c r="G31" s="170" t="n"/>
       <c r="H31" s="172" t="n"/>
-      <c r="I31" s="18" t="inlineStr">
+      <c r="I31" s="195" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12384,7 +12415,7 @@
       <c r="L31" s="172" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="67">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="195" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12392,7 +12423,7 @@
       <c r="B32" s="17" t="n"/>
       <c r="C32" s="170" t="n"/>
       <c r="D32" s="172" t="n"/>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="195" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12400,7 +12431,7 @@
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="170" t="n"/>
       <c r="H32" s="172" t="n"/>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="I32" s="195" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
